--- a/data/trans_orig/IQ09_D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D_R-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,267 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>122,28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>231,69</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>312,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>128,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>249,34</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>249,65</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>182,07</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>279,08</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>176,64</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>240,42</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>231,86</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>232,83</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>122.2809151682163</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>231.6923608662188</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>312.3825612846632</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>249.3391302101862</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>249.647986523764</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>182.0708102704962</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>279.0842735626607</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>176.6433206825027</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>240.4178244733426</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>231.8581334443128</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>232.8288106305716</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>11,04; 296,26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>106,05; 394,23</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>120,99; 472,59</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,61; 598,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>114,28; 442,59</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,67; 505,57</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20,0; 424,13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>44,42; 438,65</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149,15; 359,11</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>123,88; 413,77</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,12; 388,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>11.03895188567375</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>106.0498282794482</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>120.9862530726054</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>10.60784241331328</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>114.2805291340476</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>66.66833343326142</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>44.41721884514322</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>149.1515178529247</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>123.8808757774863</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>61.11524410688933</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>296.2640419829621</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>394.2332271544149</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>472.5895739633581</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>598.5494140661044</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>442.5850440015709</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>505.5699864625698</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>424.1262514996054</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>438.6457819574218</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>359.1093615190828</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>413.7687301021212</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>388.1479993286068</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>973,65</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>611,49</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>584,79</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>901,38</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1099,42</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>706,68</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>687,77</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1009,02</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1019,91</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>657,03</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>621,72</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>944,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>506,63; 1523,42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>327,25; 1065,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>236,45; 1002,96</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>439,4; 1540,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>507,28; 1497,35</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>301,22; 1141,29</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>359,32; 1133,91</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>388,92; 1882,89</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>689,58; 1386,38</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>434,97; 977,9</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>370,05; 1005,36</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>562,38; 1493,78</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>973.6481735645507</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>611.4907282869159</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>584.7939695532594</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>901.3794696437598</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1099.423221551464</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>706.6775570889163</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>687.7688991548902</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1009.016075871714</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1019.906832003465</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>657.0313983841098</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>621.7241183596802</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>944.1354237755635</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1546,92</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1220,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1056,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1040,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1097,49</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>980,48</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>629,17</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1010,67</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1386,11</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1070,7</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>854,92</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1026,9</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>506.6305937674924</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>327.2537488955441</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>236.4505193774035</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>439.4019449756669</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>507.2760348579877</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>301.2209421341739</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>359.3174944240198</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>388.9214812009502</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>689.5811873454176</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>434.9707070057323</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>370.0544996797314</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>562.3816916453649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>689,22; 2540,86</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36,64; 2813,57</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>495,64; 2072,88</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>470,68; 1809,46</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>224,22; 2596,12</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>336,54; 1799,61</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>89,57; 1428,12</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>390,07; 2127,13</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>700,72; 2156,01</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>487,48; 1909,22</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>405,55; 1483,14</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>600,42; 1675,72</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1523.419762906205</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1065.759462243833</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1002.958004697979</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1539.999193685002</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1497.349838404008</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1141.287495993788</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1133.912065574217</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1882.888710325375</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1386.383913630578</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>977.9007285247322</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1005.363032366383</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1493.780509258073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +919,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1712,43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1683,85</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1826,07</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2571,88</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1335,89</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1272,56</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1077,57</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2172,03</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1580,79</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1564,2</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1445,42</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2446,25</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1546.920866462499</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1220.347957649373</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1056.076150686682</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1040.287611258984</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1097.493989527453</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>980.4762272096674</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>629.1669020506677</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1010.674757618586</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1386.112689452966</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1070.703944366628</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>854.9212111915325</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1026.898312170483</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>295,79; 3927,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>827,24; 2575,83</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>559,15; 3423,68</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1698,15; 3886,06</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>51,07; 3834,65</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>654,76; 2860,37</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>334,33; 2960,93</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>654,42; 3707,23</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>563,31; 3041,53</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>952,17; 2383,83</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>771,38; 2808,31</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1608,01; 3501,6</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>689.222773776865</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>36.64211339201312</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>495.639298432282</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>470.6754737778592</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>224.216827842542</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>336.5369782362889</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>89.56633549857274</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>390.072687639252</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>700.7190138107252</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>487.480064251323</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>405.5474147864606</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>600.4177127141268</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2540.863847802268</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2813.565542657388</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2072.875115641757</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1809.46451984095</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2596.115583809318</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1799.606569493248</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1428.122206211912</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2127.129703461872</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>2156.013259571349</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1909.224991507852</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1483.137044223273</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>1675.724454606026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1712.427436478687</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1683.845855573958</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1826.07415288561</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2571.884002781611</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1335.888086083215</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1272.561631517377</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1077.5722734719</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>2172.027951269535</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1580.788570030965</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1564.204686620035</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1445.419465528523</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>2446.253345177551</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>295.7941272726666</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>827.2406382351544</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>559.1541841698917</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1698.154446340446</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>51.07074132257608</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>654.7551342056491</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>334.3344796259897</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>654.4181514083392</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>563.3056455037648</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>952.169667842301</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>771.3797906270888</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1608.012652278788</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3927.066091950438</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2575.828598912786</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3423.678652119628</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3886.059400244188</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>3834.652536653072</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2860.374957807904</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2960.93194822911</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>3707.227560833866</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>3041.531646716328</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2383.832693113499</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2808.307472591242</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>3501.600702990944</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1140,05</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1015,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>878,68</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1548,94</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>948,85</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>766,17</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>644,63</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1224,52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1068,67</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>904,17</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>770,93</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1416,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>687,48; 1792,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>667,1; 1558,09</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>556,59; 1408,77</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1073,15; 2249,67</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>507,61; 1677,19</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>513,86; 1174,61</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>417,53; 1255,2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>710,43; 1905,84</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>729,78; 1512,38</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>636,68; 1200,57</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>530,89; 1109,19</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1054,93; 1957,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1140.052331090635</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1015.572102988115</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>878.6814384510232</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1548.936425072869</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>948.8454535284831</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>766.167992932946</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>644.6346331759288</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1224.524897460577</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1068.672074903559</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>904.1696260003995</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>770.9292778379756</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1416.445268064866</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>687.4783662625334</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>667.0953950035024</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>556.5907179458264</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1073.152880172508</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>507.6127131815576</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>513.8647119367296</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>417.5331589457379</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>710.4256136466851</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>729.7814094032586</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>636.683035396911</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>530.894379708471</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1054.93426473185</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1792.193224790381</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1558.09463697483</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1408.771766777626</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2249.673011307639</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1677.189912112222</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1174.605140710644</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1255.196537176316</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1905.838597281182</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1512.383458756617</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1200.571417420908</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>1109.185444747269</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1957.542433894739</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1325,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
